--- a/email_marketing_forms/002_email_opt_in_form--email_marketing_forms.xlsx
+++ b/email_marketing_forms/002_email_opt_in_form--email_marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1116,8 +1116,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_agree',_'value':_true}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I Agree', 'value': True}</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"i_don't_agree",_'value':_false}</t>
+          <t>i_don't_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "I Don't Agree", 'value': False}</t>
+          <t>I Don't Agree</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'terms',_'value':_'terms'}</t>
+          <t>terms</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Terms', 'value': 'terms'}</t>
+          <t>Terms</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'conditions',_'value':_'conditions'}</t>
+          <t>conditions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Conditions', 'value': 'conditions'}</t>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'category_1',_'value':_'category_1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Category 1', 'value': 'category_1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'category_2',_'value':_'category_2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Category 2', 'value': 'category_2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'tag_1',_'value':_'tag_1'}</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Tag 1', 'value': 'tag_1'}</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tag_2',_'value':_'tag_2'}</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tag 2', 'value': 'tag_2'}</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_agree_again',_'value':_true}</t>
+          <t>i_agree_again</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I Agree Again', 'value': True}</t>
+          <t>I Agree Again</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"i_don't_agree_again",_'value':_false}</t>
+          <t>i_don't_agree_again</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "I Don't Agree Again", 'value': False}</t>
+          <t>I Don't Agree Again</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'another_term',_'value':_'another_term'}</t>
+          <t>another_term</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Another Term', 'value': 'another_term'}</t>
+          <t>Another Term</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'another_condition',_'value':_'another_condition'}</t>
+          <t>another_condition</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Another Condition', 'value': 'another_condition'}</t>
+          <t>Another Condition</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_agree_yet_again',_'value':_true}</t>
+          <t>i_agree_yet_again</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I Agree Yet Again', 'value': True}</t>
+          <t>I Agree Yet Again</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"i_don't_agree_yet_again",_'value':_false}</t>
+          <t>i_don't_agree_yet_again</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "I Don't Agree Yet Again", 'value': False}</t>
+          <t>I Don't Agree Yet Again</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'more_terms',_'value':_'more_terms'}</t>
+          <t>more_terms</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'More Terms', 'value': 'more_terms'}</t>
+          <t>More Terms</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'more_conditions',_'value':_'more_conditions'}</t>
+          <t>more_conditions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'More Conditions', 'value': 'more_conditions'}</t>
+          <t>More Conditions</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_agree_still_again',_'value':_true}</t>
+          <t>i_agree_still_again</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I Agree Still Again', 'value': True}</t>
+          <t>I Agree Still Again</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"i_don't_agree_still_again",_'value':_false}</t>
+          <t>i_don't_agree_still_again</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "I Don't Agree Still Again", 'value': False}</t>
+          <t>I Don't Agree Still Again</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'still_more_terms',_'value':_'still_more_terms'}</t>
+          <t>still_more_terms</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Still More Terms', 'value': 'still_more_terms'}</t>
+          <t>Still More Terms</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'still_more_conditions',_'value':_'still_more_conditions'}</t>
+          <t>still_more_conditions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Still More Conditions', 'value': 'still_more_conditions'}</t>
+          <t>Still More Conditions</t>
         </is>
       </c>
     </row>
